--- a/resultados/third_review/20260907_data2024_age.xlsx
+++ b/resultados/third_review/20260907_data2024_age.xlsx
@@ -423,13 +423,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -437,13 +437,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -451,13 +451,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>458</v>
+        <v>501</v>
       </c>
       <c r="C4" t="n">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="5">
@@ -465,13 +465,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>841</v>
+        <v>931</v>
       </c>
       <c r="C5" t="n">
-        <v>19.9</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -479,13 +479,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>905</v>
+        <v>1054</v>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>24.9</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="7">
@@ -493,13 +493,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>822</v>
+        <v>929</v>
       </c>
       <c r="C7" t="n">
-        <v>19.4</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -507,13 +507,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="C8" t="n">
-        <v>9.8</v>
+        <v>10.9</v>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="9">
@@ -521,13 +521,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="D9" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="10">
@@ -535,10 +535,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="D10"/>
     </row>
@@ -547,13 +547,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>1377</v>
+        <v>1552</v>
       </c>
       <c r="C11" t="n">
-        <v>32.5</v>
+        <v>36.7</v>
       </c>
       <c r="D11" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="12">
@@ -603,22 +603,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3763</v>
+        <v>4231</v>
       </c>
       <c r="B2" t="n">
         <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="n">
         <v>65</v>
       </c>
       <c r="E2" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
       <c r="F2" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
     </row>
   </sheetData>
